--- a/map.xlsx
+++ b/map.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/phamxuanbac/Downloads/gamedev/Game03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14943FAB-797E-BA4C-B007-9EC7DA190F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{ABB6B05F-C1F1-3F40-9587-807DB93BAFF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440"/>
   </bookViews>
   <sheets>
     <sheet name="map" sheetId="1" r:id="rId1"/>
@@ -20,9 +20,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="14">
+  <si>
+    <t>bb</t>
+  </si>
+  <si>
+    <t>r</t>
+  </si>
+  <si>
+    <t>bv</t>
+  </si>
+  <si>
+    <t>wb</t>
+  </si>
+  <si>
+    <t>wh</t>
+  </si>
+  <si>
+    <t>wv</t>
+  </si>
+  <si>
+    <t>vr</t>
+  </si>
+  <si>
+    <t>bh</t>
+  </si>
+  <si>
+    <t>399,797,812</t>
+  </si>
   <si>
     <t>358,81,809</t>
+  </si>
+  <si>
+    <t>gh</t>
+  </si>
+  <si>
+    <t>gb</t>
   </si>
   <si>
     <t>303,59,11</t>
@@ -34,7 +67,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -868,11 +901,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CV41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:DP41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A1">
         <v>1</v>
       </c>
@@ -1173,8 +1206,68 @@
       <c r="CV1">
         <v>100</v>
       </c>
+      <c r="CW1">
+        <v>101</v>
+      </c>
+      <c r="CX1">
+        <v>102</v>
+      </c>
+      <c r="CY1">
+        <v>103</v>
+      </c>
+      <c r="CZ1">
+        <v>104</v>
+      </c>
+      <c r="DA1">
+        <v>105</v>
+      </c>
+      <c r="DB1">
+        <v>106</v>
+      </c>
+      <c r="DC1">
+        <v>107</v>
+      </c>
+      <c r="DD1">
+        <v>108</v>
+      </c>
+      <c r="DE1">
+        <v>109</v>
+      </c>
+      <c r="DF1">
+        <v>110</v>
+      </c>
+      <c r="DG1">
+        <v>111</v>
+      </c>
+      <c r="DH1">
+        <v>112</v>
+      </c>
+      <c r="DI1">
+        <v>113</v>
+      </c>
+      <c r="DJ1">
+        <v>114</v>
+      </c>
+      <c r="DK1">
+        <v>115</v>
+      </c>
+      <c r="DL1">
+        <v>116</v>
+      </c>
+      <c r="DM1">
+        <v>117</v>
+      </c>
+      <c r="DN1">
+        <v>118</v>
+      </c>
+      <c r="DO1">
+        <v>119</v>
+      </c>
+      <c r="DP1">
+        <v>120</v>
+      </c>
     </row>
-    <row r="2" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1212,55 +1305,55 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD2">
         <v>128</v>
@@ -1392,70 +1485,70 @@
         <v>128</v>
       </c>
       <c r="BU2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BV2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP2">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ2">
         <v>0</v>
@@ -1476,7 +1569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1514,55 +1607,55 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD3">
         <v>128</v>
@@ -1694,70 +1787,70 @@
         <v>128</v>
       </c>
       <c r="BU3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BV3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP3">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ3">
         <v>0</v>
@@ -1778,7 +1871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>0</v>
       </c>
@@ -1816,55 +1909,55 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD4">
         <v>128</v>
@@ -1996,70 +2089,70 @@
         <v>801</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP4">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ4">
         <v>0</v>
@@ -2080,7 +2173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>0</v>
       </c>
@@ -2118,55 +2211,55 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD5">
         <v>128</v>
@@ -2247,67 +2340,67 @@
         <v>800</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP5">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ5">
         <v>0</v>
@@ -2328,7 +2421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>0</v>
       </c>
@@ -2366,55 +2459,55 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD6">
         <v>128</v>
@@ -2494,62 +2587,68 @@
       <c r="BU6">
         <v>800</v>
       </c>
+      <c r="BV6">
+        <v>128</v>
+      </c>
+      <c r="BW6">
+        <v>128</v>
+      </c>
       <c r="BX6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP6">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ6">
         <v>0</v>
@@ -2570,7 +2669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>0</v>
       </c>
@@ -2608,55 +2707,55 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD7">
         <v>128</v>
@@ -2737,67 +2836,67 @@
         <v>800</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP7">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ7">
         <v>0</v>
@@ -2818,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>0</v>
       </c>
@@ -2856,55 +2955,55 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD8">
         <v>128</v>
@@ -3000,67 +3099,67 @@
         <v>800</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP8">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ8">
         <v>0</v>
@@ -3081,7 +3180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>0</v>
       </c>
@@ -3119,55 +3218,55 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD9">
         <v>128</v>
@@ -3262,65 +3361,68 @@
       <c r="BU9">
         <v>800</v>
       </c>
+      <c r="BV9">
+        <v>128</v>
+      </c>
       <c r="BW9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP9">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ9">
         <v>0</v>
@@ -3341,7 +3443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>0</v>
       </c>
@@ -3379,55 +3481,55 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD10">
         <v>128</v>
@@ -3507,65 +3609,68 @@
       <c r="BU10">
         <v>800</v>
       </c>
+      <c r="BV10">
+        <v>128</v>
+      </c>
       <c r="BW10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP10">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ10">
         <v>0</v>
@@ -3586,7 +3691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>0</v>
       </c>
@@ -3624,55 +3729,55 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD11">
         <v>824</v>
@@ -3752,65 +3857,68 @@
       <c r="BU11">
         <v>800</v>
       </c>
+      <c r="BV11">
+        <v>128</v>
+      </c>
       <c r="BW11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CB11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CC11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CD11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CE11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CF11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CG11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CH11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CI11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CJ11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CK11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CL11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CM11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CN11">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CO11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP11">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ11">
         <v>0</v>
@@ -3831,7 +3939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>0</v>
       </c>
@@ -3869,55 +3977,55 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD12">
         <v>822</v>
@@ -4019,61 +4127,22 @@
         <v>801</v>
       </c>
       <c r="BX12">
-        <v>0</v>
-      </c>
-      <c r="BY12">
-        <v>0</v>
-      </c>
-      <c r="BZ12">
-        <v>0</v>
-      </c>
-      <c r="CA12">
-        <v>0</v>
-      </c>
-      <c r="CB12">
-        <v>0</v>
-      </c>
-      <c r="CC12">
-        <v>0</v>
-      </c>
-      <c r="CD12">
-        <v>0</v>
-      </c>
-      <c r="CE12">
-        <v>0</v>
-      </c>
-      <c r="CF12">
-        <v>0</v>
-      </c>
-      <c r="CG12">
-        <v>0</v>
-      </c>
-      <c r="CH12">
-        <v>0</v>
-      </c>
-      <c r="CI12">
-        <v>0</v>
-      </c>
-      <c r="CJ12">
-        <v>0</v>
-      </c>
-      <c r="CK12">
-        <v>0</v>
-      </c>
-      <c r="CL12">
-        <v>0</v>
-      </c>
-      <c r="CM12">
-        <v>0</v>
-      </c>
-      <c r="CN12">
+        <v>487</v>
+      </c>
+      <c r="CD12" t="s">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="s">
+        <v>1</v>
+      </c>
+      <c r="CI12" t="s">
         <v>0</v>
       </c>
       <c r="CO12">
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="CP12">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CQ12">
         <v>0</v>
@@ -4094,7 +4163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>0</v>
       </c>
@@ -4132,55 +4201,55 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD13">
         <v>128</v>
@@ -4293,56 +4362,11 @@
       <c r="BX13">
         <v>0</v>
       </c>
-      <c r="BY13">
-        <v>0</v>
-      </c>
-      <c r="BZ13">
-        <v>0</v>
-      </c>
-      <c r="CA13">
-        <v>0</v>
-      </c>
-      <c r="CB13">
-        <v>0</v>
-      </c>
-      <c r="CC13">
-        <v>0</v>
-      </c>
-      <c r="CD13">
-        <v>0</v>
-      </c>
-      <c r="CE13">
-        <v>0</v>
-      </c>
-      <c r="CF13">
-        <v>0</v>
-      </c>
-      <c r="CG13">
-        <v>0</v>
-      </c>
-      <c r="CH13">
-        <v>0</v>
-      </c>
-      <c r="CI13">
-        <v>0</v>
-      </c>
-      <c r="CJ13">
-        <v>0</v>
-      </c>
-      <c r="CK13">
-        <v>0</v>
-      </c>
-      <c r="CL13">
-        <v>0</v>
-      </c>
-      <c r="CM13">
-        <v>0</v>
-      </c>
-      <c r="CN13">
-        <v>0</v>
-      </c>
-      <c r="CO13">
-        <v>0</v>
+      <c r="CD13" t="s">
+        <v>2</v>
+      </c>
+      <c r="CI13" t="s">
+        <v>2</v>
       </c>
       <c r="CP13">
         <v>0</v>
@@ -4366,7 +4390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>0</v>
       </c>
@@ -4404,55 +4428,55 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD14">
         <v>128</v>
@@ -4562,56 +4586,11 @@
       <c r="BX14">
         <v>0</v>
       </c>
-      <c r="BY14">
-        <v>0</v>
-      </c>
-      <c r="BZ14">
-        <v>0</v>
-      </c>
-      <c r="CA14">
-        <v>0</v>
-      </c>
-      <c r="CB14">
-        <v>0</v>
-      </c>
-      <c r="CC14">
-        <v>0</v>
-      </c>
-      <c r="CD14">
-        <v>0</v>
-      </c>
-      <c r="CE14">
-        <v>0</v>
-      </c>
-      <c r="CF14">
-        <v>0</v>
-      </c>
-      <c r="CG14">
-        <v>0</v>
-      </c>
-      <c r="CH14">
-        <v>0</v>
-      </c>
-      <c r="CI14">
-        <v>0</v>
-      </c>
-      <c r="CJ14">
-        <v>0</v>
-      </c>
-      <c r="CK14">
-        <v>0</v>
-      </c>
-      <c r="CL14">
-        <v>0</v>
-      </c>
-      <c r="CM14">
-        <v>0</v>
-      </c>
-      <c r="CN14">
-        <v>0</v>
-      </c>
-      <c r="CO14">
-        <v>0</v>
+      <c r="CD14" t="s">
+        <v>2</v>
+      </c>
+      <c r="CI14" t="s">
+        <v>2</v>
       </c>
       <c r="CP14">
         <v>0</v>
@@ -4635,7 +4614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>0</v>
       </c>
@@ -4673,55 +4652,55 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD15">
         <v>128</v>
@@ -4817,67 +4796,37 @@
         <v>40</v>
       </c>
       <c r="BV15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BW15">
+        <v>23</v>
+      </c>
+      <c r="BX15">
+        <v>24</v>
+      </c>
+      <c r="BY15">
+        <v>25</v>
+      </c>
+      <c r="CD15" t="s">
         <v>2</v>
       </c>
-      <c r="BX15">
+      <c r="CI15" t="s">
+        <v>0</v>
+      </c>
+      <c r="CL15">
+        <v>20</v>
+      </c>
+      <c r="CM15">
+        <v>21</v>
+      </c>
+      <c r="CN15">
+        <v>22</v>
+      </c>
+      <c r="CO15">
         <v>3</v>
       </c>
-      <c r="BY15">
-        <v>0</v>
-      </c>
-      <c r="BZ15">
-        <v>0</v>
-      </c>
-      <c r="CA15">
-        <v>0</v>
-      </c>
-      <c r="CB15">
-        <v>0</v>
-      </c>
-      <c r="CC15">
-        <v>0</v>
-      </c>
-      <c r="CD15">
-        <v>0</v>
-      </c>
-      <c r="CE15">
-        <v>0</v>
-      </c>
-      <c r="CF15">
-        <v>0</v>
-      </c>
-      <c r="CG15">
-        <v>0</v>
-      </c>
-      <c r="CH15">
-        <v>0</v>
-      </c>
-      <c r="CI15">
-        <v>0</v>
-      </c>
-      <c r="CJ15">
-        <v>0</v>
-      </c>
-      <c r="CK15">
-        <v>0</v>
-      </c>
-      <c r="CL15">
-        <v>0</v>
-      </c>
-      <c r="CM15">
-        <v>0</v>
-      </c>
-      <c r="CN15">
-        <v>0</v>
-      </c>
-      <c r="CO15">
-        <v>0</v>
-      </c>
       <c r="CP15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CQ15">
         <v>0</v>
@@ -4898,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:100" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:120" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>0</v>
       </c>
@@ -4936,55 +4885,55 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD16">
         <v>128</v>
@@ -5089,64 +5038,52 @@
         <v>128</v>
       </c>
       <c r="BW16">
-        <v>128</v>
+        <v>43</v>
       </c>
       <c r="BX16">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="BY16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BZ16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CA16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CB16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CC16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CD16">
-        <v>0</v>
-      </c>
-      <c r="CE16">
-        <v>0</v>
-      </c>
-      <c r="CF16">
-        <v>0</v>
-      </c>
-      <c r="CG16">
-        <v>0</v>
-      </c>
-      <c r="CH16">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="CI16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CJ16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CK16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CM16">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="CN16">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="CO16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ16">
         <v>0</v>
@@ -5205,55 +5142,55 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD17">
         <v>128</v>
@@ -5367,58 +5304,46 @@
         <v>128</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD17">
-        <v>0</v>
-      </c>
-      <c r="CE17">
-        <v>0</v>
-      </c>
-      <c r="CF17">
-        <v>0</v>
-      </c>
-      <c r="CG17">
-        <v>0</v>
-      </c>
-      <c r="CH17">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="CI17">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CJ17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ17">
         <v>0</v>
@@ -5477,55 +5402,55 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD18">
         <v>128</v>
@@ -5645,58 +5570,58 @@
         <v>128</v>
       </c>
       <c r="BY18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ18">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CA18">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CB18">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CC18">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CD18">
-        <v>0</v>
-      </c>
-      <c r="CE18">
-        <v>0</v>
-      </c>
-      <c r="CF18">
-        <v>0</v>
-      </c>
-      <c r="CG18">
-        <v>0</v>
-      </c>
-      <c r="CH18">
-        <v>0</v>
+        <v>487</v>
+      </c>
+      <c r="CE18" t="s">
+        <v>3</v>
+      </c>
+      <c r="CF18" t="s">
+        <v>4</v>
+      </c>
+      <c r="CG18" t="s">
+        <v>4</v>
+      </c>
+      <c r="CH18" t="s">
+        <v>3</v>
       </c>
       <c r="CI18">
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="CJ18">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CK18">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CL18">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CM18">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CN18">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CO18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ18">
         <v>0</v>
@@ -5755,100 +5680,100 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AS19">
         <v>128</v>
@@ -5917,58 +5842,19 @@
         <v>128</v>
       </c>
       <c r="BY19">
-        <v>0</v>
-      </c>
-      <c r="BZ19">
-        <v>0</v>
-      </c>
-      <c r="CA19">
-        <v>0</v>
-      </c>
-      <c r="CB19">
-        <v>0</v>
-      </c>
-      <c r="CC19">
-        <v>0</v>
-      </c>
-      <c r="CD19">
-        <v>0</v>
-      </c>
-      <c r="CE19">
-        <v>0</v>
-      </c>
-      <c r="CF19">
-        <v>0</v>
-      </c>
-      <c r="CG19">
-        <v>0</v>
-      </c>
-      <c r="CH19">
-        <v>0</v>
-      </c>
-      <c r="CI19">
-        <v>0</v>
-      </c>
-      <c r="CJ19">
-        <v>0</v>
-      </c>
-      <c r="CK19">
-        <v>0</v>
-      </c>
-      <c r="CL19">
-        <v>0</v>
-      </c>
-      <c r="CM19">
-        <v>0</v>
-      </c>
-      <c r="CN19">
+        <v>50</v>
+      </c>
+      <c r="CD19" t="s">
+        <v>3</v>
+      </c>
+      <c r="CI19" t="s">
         <v>0</v>
       </c>
       <c r="CO19">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ19">
         <v>0</v>
@@ -6027,100 +5913,100 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AS20">
         <v>128</v>
@@ -6189,58 +6075,19 @@
         <v>128</v>
       </c>
       <c r="BY20">
-        <v>0</v>
-      </c>
-      <c r="BZ20">
-        <v>0</v>
-      </c>
-      <c r="CA20">
-        <v>0</v>
-      </c>
-      <c r="CB20">
-        <v>0</v>
-      </c>
-      <c r="CC20">
-        <v>0</v>
-      </c>
-      <c r="CD20">
-        <v>0</v>
-      </c>
-      <c r="CE20">
-        <v>0</v>
-      </c>
-      <c r="CF20">
-        <v>0</v>
-      </c>
-      <c r="CG20">
-        <v>0</v>
-      </c>
-      <c r="CH20">
-        <v>0</v>
-      </c>
-      <c r="CI20">
-        <v>0</v>
-      </c>
-      <c r="CJ20">
-        <v>0</v>
-      </c>
-      <c r="CK20">
-        <v>0</v>
-      </c>
-      <c r="CL20">
-        <v>0</v>
-      </c>
-      <c r="CM20">
-        <v>0</v>
-      </c>
-      <c r="CN20">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="CD20" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI20" t="s">
+        <v>2</v>
       </c>
       <c r="CO20">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ20">
         <v>0</v>
@@ -6299,100 +6146,100 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AS21">
         <v>128</v>
@@ -6461,58 +6308,19 @@
         <v>128</v>
       </c>
       <c r="BY21">
-        <v>0</v>
-      </c>
-      <c r="BZ21">
-        <v>0</v>
-      </c>
-      <c r="CA21">
-        <v>0</v>
-      </c>
-      <c r="CB21">
-        <v>0</v>
-      </c>
-      <c r="CC21">
-        <v>0</v>
-      </c>
-      <c r="CD21">
-        <v>0</v>
-      </c>
-      <c r="CE21">
-        <v>0</v>
-      </c>
-      <c r="CF21">
-        <v>0</v>
-      </c>
-      <c r="CG21">
-        <v>0</v>
-      </c>
-      <c r="CH21">
-        <v>0</v>
-      </c>
-      <c r="CI21">
-        <v>0</v>
-      </c>
-      <c r="CJ21">
-        <v>0</v>
-      </c>
-      <c r="CK21">
-        <v>0</v>
-      </c>
-      <c r="CL21">
-        <v>0</v>
-      </c>
-      <c r="CM21">
-        <v>0</v>
-      </c>
-      <c r="CN21">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="CD21" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI21" t="s">
+        <v>2</v>
       </c>
       <c r="CO21">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ21">
         <v>0</v>
@@ -6535,136 +6343,136 @@
     </row>
     <row r="22" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AI22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AN22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AP22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AQ22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AR22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AS22">
         <v>128</v>
@@ -6733,58 +6541,25 @@
         <v>128</v>
       </c>
       <c r="BY22">
-        <v>0</v>
-      </c>
-      <c r="BZ22">
-        <v>0</v>
-      </c>
-      <c r="CA22">
-        <v>0</v>
-      </c>
-      <c r="CB22">
-        <v>0</v>
-      </c>
-      <c r="CC22">
-        <v>0</v>
-      </c>
-      <c r="CD22">
-        <v>0</v>
-      </c>
-      <c r="CE22">
-        <v>0</v>
-      </c>
-      <c r="CF22">
-        <v>0</v>
-      </c>
-      <c r="CG22">
-        <v>0</v>
-      </c>
-      <c r="CH22">
-        <v>0</v>
-      </c>
-      <c r="CI22">
-        <v>0</v>
-      </c>
-      <c r="CJ22">
-        <v>0</v>
-      </c>
-      <c r="CK22">
-        <v>0</v>
-      </c>
-      <c r="CL22">
-        <v>0</v>
-      </c>
-      <c r="CM22">
-        <v>0</v>
-      </c>
-      <c r="CN22">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="CC22" t="s">
+        <v>6</v>
+      </c>
+      <c r="CD22" t="s">
+        <v>3</v>
+      </c>
+      <c r="CI22" t="s">
+        <v>0</v>
+      </c>
+      <c r="CJ22" t="s">
+        <v>1</v>
       </c>
       <c r="CO22">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ22">
         <v>0</v>
@@ -6807,37 +6582,37 @@
     </row>
     <row r="23" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="J23">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="K23">
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="L23">
         <v>128</v>
@@ -6981,58 +6756,46 @@
         <v>128</v>
       </c>
       <c r="BY23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CA23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CB23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CC23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD23">
-        <v>0</v>
-      </c>
-      <c r="CE23">
-        <v>0</v>
-      </c>
-      <c r="CF23">
-        <v>0</v>
-      </c>
-      <c r="CG23">
-        <v>0</v>
-      </c>
-      <c r="CH23">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="CI23">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="CJ23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CK23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CL23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CM23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CN23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CO23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ23">
         <v>0</v>
@@ -7055,31 +6818,31 @@
     </row>
     <row r="24" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I24">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="J24">
         <v>128</v>
@@ -7229,58 +6992,58 @@
         <v>128</v>
       </c>
       <c r="BY24">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="BZ24">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CA24">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CB24">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CC24">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CD24">
-        <v>0</v>
-      </c>
-      <c r="CE24">
-        <v>0</v>
-      </c>
-      <c r="CF24">
-        <v>0</v>
-      </c>
-      <c r="CG24">
-        <v>0</v>
-      </c>
-      <c r="CH24">
+        <v>487</v>
+      </c>
+      <c r="CE24" t="s">
+        <v>0</v>
+      </c>
+      <c r="CF24" t="s">
+        <v>7</v>
+      </c>
+      <c r="CG24" t="s">
+        <v>7</v>
+      </c>
+      <c r="CH24" t="s">
         <v>0</v>
       </c>
       <c r="CI24">
-        <v>0</v>
+        <v>802</v>
       </c>
       <c r="CJ24">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CK24">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CL24">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CM24">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CN24">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="CO24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ24">
         <v>0</v>
@@ -7303,28 +7066,28 @@
     </row>
     <row r="25" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G25">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="H25">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="I25">
         <v>128</v>
@@ -7474,61 +7237,19 @@
         <v>128</v>
       </c>
       <c r="BX25">
-        <v>128</v>
-      </c>
-      <c r="BY25">
-        <v>0</v>
-      </c>
-      <c r="BZ25">
-        <v>0</v>
-      </c>
-      <c r="CA25">
-        <v>0</v>
-      </c>
-      <c r="CB25">
-        <v>0</v>
-      </c>
-      <c r="CC25">
-        <v>0</v>
-      </c>
-      <c r="CD25">
-        <v>0</v>
-      </c>
-      <c r="CE25">
-        <v>0</v>
-      </c>
-      <c r="CF25">
-        <v>0</v>
-      </c>
-      <c r="CG25">
-        <v>0</v>
-      </c>
-      <c r="CH25">
-        <v>0</v>
-      </c>
-      <c r="CI25">
-        <v>0</v>
-      </c>
-      <c r="CJ25">
-        <v>0</v>
-      </c>
-      <c r="CK25">
-        <v>0</v>
-      </c>
-      <c r="CL25">
-        <v>0</v>
-      </c>
-      <c r="CM25">
-        <v>0</v>
-      </c>
-      <c r="CN25">
+        <v>50</v>
+      </c>
+      <c r="CD25" t="s">
+        <v>3</v>
+      </c>
+      <c r="CI25" t="s">
         <v>0</v>
       </c>
       <c r="CO25">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP25">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ25">
         <v>0</v>
@@ -7551,25 +7272,25 @@
     </row>
     <row r="26" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F26">
-        <v>102.129</v>
+        <v>128</v>
       </c>
       <c r="G26">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H26">
         <v>128</v>
@@ -7722,61 +7443,19 @@
         <v>128</v>
       </c>
       <c r="BX26">
-        <v>128</v>
-      </c>
-      <c r="BY26">
-        <v>0</v>
-      </c>
-      <c r="BZ26">
-        <v>0</v>
-      </c>
-      <c r="CA26">
-        <v>0</v>
-      </c>
-      <c r="CB26">
-        <v>0</v>
-      </c>
-      <c r="CC26">
-        <v>0</v>
-      </c>
-      <c r="CD26">
-        <v>0</v>
-      </c>
-      <c r="CE26">
-        <v>0</v>
-      </c>
-      <c r="CF26">
-        <v>0</v>
-      </c>
-      <c r="CG26">
-        <v>0</v>
-      </c>
-      <c r="CH26">
-        <v>0</v>
-      </c>
-      <c r="CI26">
-        <v>0</v>
-      </c>
-      <c r="CJ26">
-        <v>0</v>
-      </c>
-      <c r="CK26">
-        <v>0</v>
-      </c>
-      <c r="CL26">
-        <v>0</v>
-      </c>
-      <c r="CM26">
-        <v>0</v>
-      </c>
-      <c r="CN26">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="CD26" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI26" t="s">
+        <v>2</v>
       </c>
       <c r="CO26">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP26">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ26">
         <v>0</v>
@@ -7799,22 +7478,22 @@
     </row>
     <row r="27" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B27">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C27">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="D27">
-        <v>82</v>
+        <v>128</v>
       </c>
       <c r="E27">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="F27">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G27">
         <v>128</v>
@@ -7928,7 +7607,7 @@
         <v>419.80700000000002</v>
       </c>
       <c r="AR27">
-        <v>804</v>
+        <v>359.80399999999997</v>
       </c>
       <c r="AS27">
         <v>128</v>
@@ -7988,61 +7667,19 @@
         <v>128</v>
       </c>
       <c r="BX27">
-        <v>128</v>
-      </c>
-      <c r="BY27">
-        <v>0</v>
-      </c>
-      <c r="BZ27">
-        <v>0</v>
-      </c>
-      <c r="CA27">
-        <v>0</v>
-      </c>
-      <c r="CB27">
-        <v>0</v>
-      </c>
-      <c r="CC27">
-        <v>0</v>
-      </c>
-      <c r="CD27">
-        <v>0</v>
-      </c>
-      <c r="CE27">
-        <v>0</v>
-      </c>
-      <c r="CF27">
-        <v>0</v>
-      </c>
-      <c r="CG27">
-        <v>0</v>
-      </c>
-      <c r="CH27">
-        <v>0</v>
-      </c>
-      <c r="CI27">
-        <v>0</v>
-      </c>
-      <c r="CJ27">
-        <v>0</v>
-      </c>
-      <c r="CK27">
-        <v>0</v>
-      </c>
-      <c r="CL27">
-        <v>0</v>
-      </c>
-      <c r="CM27">
-        <v>0</v>
-      </c>
-      <c r="CN27">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="CD27" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI27" t="s">
+        <v>2</v>
       </c>
       <c r="CO27">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP27">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ27">
         <v>0</v>
@@ -8065,10 +7702,10 @@
     </row>
     <row r="28" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B28">
-        <v>804</v>
+        <v>128</v>
       </c>
       <c r="C28">
         <v>128</v>
@@ -8197,10 +7834,10 @@
         <v>357.803</v>
       </c>
       <c r="AS28">
-        <v>799</v>
-      </c>
-      <c r="AT28">
-        <v>797.81200000000001</v>
+        <v>398.79899999999998</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>8</v>
       </c>
       <c r="AU28">
         <v>813</v>
@@ -8254,61 +7891,22 @@
         <v>128</v>
       </c>
       <c r="BX28">
-        <v>128</v>
-      </c>
-      <c r="BY28">
-        <v>0</v>
-      </c>
-      <c r="BZ28">
-        <v>0</v>
-      </c>
-      <c r="CA28">
-        <v>0</v>
-      </c>
-      <c r="CB28">
-        <v>0</v>
-      </c>
-      <c r="CC28">
-        <v>0</v>
-      </c>
-      <c r="CD28">
-        <v>0</v>
-      </c>
-      <c r="CE28">
-        <v>0</v>
-      </c>
-      <c r="CF28">
-        <v>0</v>
-      </c>
-      <c r="CG28">
-        <v>0</v>
-      </c>
-      <c r="CH28">
-        <v>0</v>
-      </c>
-      <c r="CI28">
-        <v>0</v>
-      </c>
-      <c r="CJ28">
-        <v>0</v>
-      </c>
-      <c r="CK28">
-        <v>0</v>
-      </c>
-      <c r="CL28">
-        <v>0</v>
-      </c>
-      <c r="CM28">
-        <v>0</v>
-      </c>
-      <c r="CN28">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="CD28" t="s">
+        <v>3</v>
+      </c>
+      <c r="CI28" t="s">
+        <v>0</v>
+      </c>
+      <c r="CJ28" t="s">
+        <v>6</v>
       </c>
       <c r="CO28">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP28">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ28">
         <v>0</v>
@@ -8331,10 +7929,10 @@
     </row>
     <row r="29" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B29">
-        <v>805.803</v>
+        <v>128</v>
       </c>
       <c r="C29">
         <v>128</v>
@@ -8394,7 +7992,7 @@
         <v>808</v>
       </c>
       <c r="V29" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>356.81099999999998</v>
@@ -8463,22 +8061,22 @@
         <v>355</v>
       </c>
       <c r="AS29">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="AT29">
-        <v>814</v>
+        <v>359.81400000000002</v>
       </c>
       <c r="AU29">
         <v>815</v>
       </c>
       <c r="AV29">
-        <v>816</v>
+        <v>398.81599999999997</v>
       </c>
       <c r="AW29">
-        <v>794</v>
+        <v>357.79399999999998</v>
       </c>
       <c r="AX29">
-        <v>789</v>
+        <v>399.78899999999999</v>
       </c>
       <c r="AY29">
         <v>801</v>
@@ -8514,67 +8112,67 @@
         <v>802</v>
       </c>
       <c r="BV29">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="BW29">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="BX29">
-        <v>0</v>
-      </c>
-      <c r="BY29">
-        <v>0</v>
-      </c>
-      <c r="BZ29">
-        <v>0</v>
-      </c>
-      <c r="CA29">
-        <v>0</v>
-      </c>
-      <c r="CB29">
-        <v>0</v>
-      </c>
-      <c r="CC29">
-        <v>0</v>
-      </c>
-      <c r="CD29">
-        <v>0</v>
-      </c>
-      <c r="CE29">
-        <v>0</v>
-      </c>
-      <c r="CF29">
-        <v>0</v>
-      </c>
-      <c r="CG29">
-        <v>0</v>
-      </c>
-      <c r="CH29">
-        <v>0</v>
-      </c>
-      <c r="CI29">
-        <v>0</v>
-      </c>
-      <c r="CJ29">
-        <v>0</v>
-      </c>
-      <c r="CK29">
-        <v>0</v>
-      </c>
-      <c r="CL29">
-        <v>0</v>
-      </c>
-      <c r="CM29">
-        <v>0</v>
-      </c>
-      <c r="CN29">
-        <v>0</v>
+        <v>487</v>
+      </c>
+      <c r="BY29" t="s">
+        <v>10</v>
+      </c>
+      <c r="BZ29" t="s">
+        <v>0</v>
+      </c>
+      <c r="CA29" t="s">
+        <v>7</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>7</v>
+      </c>
+      <c r="CC29" t="s">
+        <v>0</v>
+      </c>
+      <c r="CD29" t="s">
+        <v>11</v>
+      </c>
+      <c r="CE29" t="s">
+        <v>3</v>
+      </c>
+      <c r="CF29" t="s">
+        <v>4</v>
+      </c>
+      <c r="CG29" t="s">
+        <v>4</v>
+      </c>
+      <c r="CH29" t="s">
+        <v>3</v>
+      </c>
+      <c r="CI29" t="s">
+        <v>11</v>
+      </c>
+      <c r="CJ29" t="s">
+        <v>0</v>
+      </c>
+      <c r="CK29" t="s">
+        <v>7</v>
+      </c>
+      <c r="CL29" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM29" t="s">
+        <v>0</v>
+      </c>
+      <c r="CN29" t="s">
+        <v>10</v>
       </c>
       <c r="CO29">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP29">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ29">
         <v>0</v>
@@ -8597,10 +8195,10 @@
     </row>
     <row r="30" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B30">
-        <v>107.80500000000001</v>
+        <v>128</v>
       </c>
       <c r="C30">
         <v>50</v>
@@ -8729,22 +8327,22 @@
         <v>356</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="AT30">
         <v>817</v>
       </c>
       <c r="AU30">
-        <v>818</v>
+        <v>359.81799999999998</v>
       </c>
       <c r="AV30">
-        <v>819</v>
+        <v>359.81900000000002</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="AY30">
         <v>156</v>
@@ -8776,71 +8374,23 @@
       <c r="BO30">
         <v>133</v>
       </c>
-      <c r="BU30">
-        <v>0</v>
-      </c>
-      <c r="BV30">
-        <v>0</v>
-      </c>
-      <c r="BW30">
-        <v>0</v>
-      </c>
-      <c r="BX30">
-        <v>0</v>
-      </c>
-      <c r="BY30">
-        <v>0</v>
-      </c>
-      <c r="BZ30">
-        <v>0</v>
-      </c>
-      <c r="CA30">
-        <v>0</v>
-      </c>
-      <c r="CB30">
-        <v>0</v>
-      </c>
-      <c r="CC30">
-        <v>0</v>
-      </c>
-      <c r="CD30">
-        <v>0</v>
-      </c>
-      <c r="CE30">
-        <v>0</v>
-      </c>
-      <c r="CF30">
-        <v>0</v>
-      </c>
-      <c r="CG30">
-        <v>0</v>
-      </c>
-      <c r="CH30">
-        <v>0</v>
-      </c>
-      <c r="CI30">
-        <v>0</v>
-      </c>
-      <c r="CJ30">
-        <v>0</v>
-      </c>
-      <c r="CK30">
-        <v>0</v>
-      </c>
-      <c r="CL30">
-        <v>0</v>
-      </c>
-      <c r="CM30">
-        <v>0</v>
-      </c>
-      <c r="CN30">
-        <v>0</v>
+      <c r="CC30" t="s">
+        <v>1</v>
+      </c>
+      <c r="CD30" t="s">
+        <v>3</v>
+      </c>
+      <c r="CI30" t="s">
+        <v>3</v>
+      </c>
+      <c r="CJ30" t="s">
+        <v>1</v>
       </c>
       <c r="CO30">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP30">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ30">
         <v>0</v>
@@ -8863,7 +8413,7 @@
     </row>
     <row r="31" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A31">
-        <v>805</v>
+        <v>128</v>
       </c>
       <c r="B31">
         <v>128</v>
@@ -8887,7 +8437,7 @@
         <v>225</v>
       </c>
       <c r="I31">
-        <v>226.34</v>
+        <v>226.34100000000001</v>
       </c>
       <c r="J31">
         <v>227</v>
@@ -8989,28 +8539,28 @@
         <v>185</v>
       </c>
       <c r="AQ31">
-        <v>186</v>
+        <v>359.18599999999998</v>
       </c>
       <c r="AR31">
         <v>356.18700000000001</v>
       </c>
       <c r="AS31">
-        <v>188</v>
+        <v>418.18799999999999</v>
       </c>
       <c r="AT31">
-        <v>189</v>
+        <v>356.18900000000002</v>
       </c>
       <c r="AU31">
-        <v>783</v>
+        <v>355.78300000000002</v>
       </c>
       <c r="AV31">
-        <v>5</v>
+        <v>355.5</v>
       </c>
       <c r="AW31">
-        <v>11</v>
+        <v>399.11</v>
       </c>
       <c r="AX31">
-        <v>12</v>
+        <v>355.12</v>
       </c>
       <c r="AY31">
         <v>154.4</v>
@@ -9042,71 +8592,17 @@
       <c r="BO31">
         <v>153</v>
       </c>
-      <c r="BU31">
-        <v>0</v>
-      </c>
-      <c r="BV31">
-        <v>0</v>
-      </c>
-      <c r="BW31">
-        <v>0</v>
-      </c>
-      <c r="BX31">
-        <v>0</v>
-      </c>
-      <c r="BY31">
-        <v>0</v>
-      </c>
-      <c r="BZ31">
-        <v>0</v>
-      </c>
-      <c r="CA31">
-        <v>0</v>
-      </c>
-      <c r="CB31">
-        <v>0</v>
-      </c>
-      <c r="CC31">
-        <v>0</v>
-      </c>
-      <c r="CD31">
-        <v>0</v>
-      </c>
-      <c r="CE31">
-        <v>0</v>
-      </c>
-      <c r="CF31">
-        <v>0</v>
-      </c>
-      <c r="CG31">
-        <v>0</v>
-      </c>
-      <c r="CH31">
-        <v>0</v>
-      </c>
-      <c r="CI31">
-        <v>0</v>
-      </c>
-      <c r="CJ31">
-        <v>0</v>
-      </c>
-      <c r="CK31">
-        <v>0</v>
-      </c>
-      <c r="CL31">
-        <v>0</v>
-      </c>
-      <c r="CM31">
-        <v>0</v>
-      </c>
-      <c r="CN31">
-        <v>0</v>
+      <c r="CD31" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI31" t="s">
+        <v>5</v>
       </c>
       <c r="CO31">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="CP31">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ31">
         <v>0</v>
@@ -9129,10 +8625,10 @@
     </row>
     <row r="32" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B32">
-        <v>804</v>
+        <v>128</v>
       </c>
       <c r="C32">
         <v>50</v>
@@ -9302,9 +8798,6 @@
       <c r="BF32">
         <v>25</v>
       </c>
-      <c r="BG32">
-        <v>0</v>
-      </c>
       <c r="BH32">
         <v>171</v>
       </c>
@@ -9336,67 +8829,43 @@
         <v>3</v>
       </c>
       <c r="BV32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BW32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BX32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BY32">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BZ32">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA32">
-        <v>0</v>
-      </c>
-      <c r="CB32">
-        <v>0</v>
-      </c>
-      <c r="CC32">
-        <v>0</v>
-      </c>
-      <c r="CD32">
-        <v>0</v>
-      </c>
-      <c r="CE32">
-        <v>0</v>
-      </c>
-      <c r="CF32">
-        <v>0</v>
-      </c>
-      <c r="CG32">
-        <v>0</v>
-      </c>
-      <c r="CH32">
-        <v>0</v>
-      </c>
-      <c r="CI32">
-        <v>0</v>
-      </c>
-      <c r="CJ32">
-        <v>0</v>
-      </c>
-      <c r="CK32">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="CD32" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI32" t="s">
+        <v>5</v>
       </c>
       <c r="CL32">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="CM32">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CN32">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="CO32">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP32">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ32">
         <v>0</v>
@@ -9419,10 +8888,10 @@
     </row>
     <row r="33" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B33">
-        <v>803</v>
+        <v>128</v>
       </c>
       <c r="C33">
         <v>50</v>
@@ -9638,67 +9107,67 @@
         <v>128</v>
       </c>
       <c r="BV33">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW33">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX33">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY33">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="BZ33">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="CA33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CB33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CC33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CD33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CH33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CI33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CJ33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CK33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CM33">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="CN33">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="CO33">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP33">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ33">
         <v>0</v>
@@ -9721,10 +9190,10 @@
     </row>
     <row r="34" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B34">
-        <v>805</v>
+        <v>128</v>
       </c>
       <c r="C34">
         <v>50</v>
@@ -9940,67 +9409,67 @@
         <v>128</v>
       </c>
       <c r="BV34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP34">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ34">
         <v>0</v>
@@ -10023,10 +9492,10 @@
     </row>
     <row r="35" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B35">
-        <v>805.10900000000004</v>
+        <v>128</v>
       </c>
       <c r="C35">
         <v>50</v>
@@ -10242,67 +9711,67 @@
         <v>128</v>
       </c>
       <c r="BV35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP35">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ35">
         <v>0</v>
@@ -10325,10 +9794,10 @@
     </row>
     <row r="36" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B36">
-        <v>129.80500000000001</v>
+        <v>128</v>
       </c>
       <c r="C36">
         <v>50</v>
@@ -10544,67 +10013,67 @@
         <v>128</v>
       </c>
       <c r="BV36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP36">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ36">
         <v>0</v>
@@ -10627,10 +10096,10 @@
     </row>
     <row r="37" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B37">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C37">
         <v>50</v>
@@ -10639,7 +10108,7 @@
         <v>301.89999999999998</v>
       </c>
       <c r="E37" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F37">
         <v>304.12</v>
@@ -10678,7 +10147,7 @@
         <v>304.11</v>
       </c>
       <c r="R37" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="S37">
         <v>306.89999999999998</v>
@@ -10846,67 +10315,67 @@
         <v>128</v>
       </c>
       <c r="BV37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP37">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ37">
         <v>0</v>
@@ -10929,7 +10398,7 @@
     </row>
     <row r="38" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>805.12900000000002</v>
+        <v>128</v>
       </c>
       <c r="B38">
         <v>128</v>
@@ -11148,67 +10617,67 @@
         <v>128</v>
       </c>
       <c r="BV38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP38">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ38">
         <v>0</v>
@@ -11231,7 +10700,7 @@
     </row>
     <row r="39" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B39">
         <v>128</v>
@@ -11246,19 +10715,19 @@
         <v>128</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="K39">
         <v>128</v>
@@ -11450,67 +10919,67 @@
         <v>128</v>
       </c>
       <c r="BV39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP39">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ39">
         <v>0</v>
@@ -11533,37 +11002,37 @@
     </row>
     <row r="40" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="L40">
         <v>128</v>
@@ -11752,67 +11221,67 @@
         <v>128</v>
       </c>
       <c r="BV40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP40">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ40">
         <v>0</v>
@@ -11835,286 +11304,286 @@
     </row>
     <row r="41" spans="1:100" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AL41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AM41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AO41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AP41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AU41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AV41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AW41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AX41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AY41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="AZ41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BA41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BB41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BC41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BD41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BE41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BF41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BG41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BH41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BI41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BJ41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BK41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BL41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BM41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BN41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BO41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BP41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BQ41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BR41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BS41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BT41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BU41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BV41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BZ41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CA41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CB41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CC41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CD41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CE41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CF41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CG41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CH41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CI41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CJ41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CK41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CL41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CM41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CN41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CO41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CP41">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="CQ41">
         <v>0</v>
